--- a/Table_S3.xlsx
+++ b/Table_S3.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S3_AP2ERF_gained" sheetId="1" r:id="R1825ff8e110d437a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S3_AP2ERF_gained" sheetId="1" r:id="R10e7db0935534e32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -326,10 +326,10 @@
     <x:col min="1" max="1" width="34" style="13" customWidth="1"/>
     <x:col min="2" max="2" width="18" style="13" customWidth="1"/>
     <x:col min="3" max="3" width="18" style="13" customWidth="1"/>
-    <x:col min="4" max="4" width="18" style="13" customWidth="1"/>
+    <x:col min="4" max="4" width="19" style="13" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" style="13" customWidth="1"/>
-    <x:col min="6" max="6" width="18" style="13" customWidth="1"/>
-    <x:col min="7" max="7" width="18" style="13" customWidth="1"/>
+    <x:col min="6" max="6" width="23" style="13" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" style="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="13" customFormat="1" ht="36" customHeight="1">
@@ -359,10 +359,8 @@
           <x:t xml:space="preserve">Native best score</x:t>
         </x:is>
       </x:c>
-      <x:c r="D2" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mutated best score</x:t>
-        </x:is>
+      <x:c r="D2" s="10" t="str">
+        <x:v>Designed HSE-disrupted best score</x:v>
       </x:c>
       <x:c r="E2" s="10" t="inlineStr">
         <x:is>
@@ -374,10 +372,8 @@
           <x:t xml:space="preserve">Effect class</x:t>
         </x:is>
       </x:c>
-      <x:c r="G2" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mutated best match</x:t>
-        </x:is>
+      <x:c r="G2" s="10" t="str">
+        <x:v>Designed HSE-disrupted best match</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -400,10 +396,8 @@
       <x:c r="E3" s="12" t="n">
         <x:v>0.222</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F3" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G3" s="12" t="inlineStr">
         <x:is>
@@ -431,10 +425,8 @@
       <x:c r="E4" s="12" t="n">
         <x:v>0.192</x:v>
       </x:c>
-      <x:c r="F4" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F4" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G4" s="12" t="inlineStr">
         <x:is>
@@ -462,10 +454,8 @@
       <x:c r="E5" s="12" t="n">
         <x:v>0.252</x:v>
       </x:c>
-      <x:c r="F5" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F5" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G5" s="12" t="inlineStr">
         <x:is>
@@ -493,10 +483,8 @@
       <x:c r="E6" s="12" t="n">
         <x:v>0.0626</x:v>
       </x:c>
-      <x:c r="F6" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">strengthened_after_mutation</x:t>
-        </x:is>
+      <x:c r="F6" s="12" t="str">
+        <x:v>strengthened_in_design</x:v>
       </x:c>
       <x:c r="G6" s="12" t="inlineStr">
         <x:is>
@@ -524,10 +512,8 @@
       <x:c r="E7" s="12" t="n">
         <x:v>0.242</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F7" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G7" s="12" t="inlineStr">
         <x:is>
@@ -555,10 +541,8 @@
       <x:c r="E8" s="12" t="n">
         <x:v>0.247</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F8" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G8" s="12" t="inlineStr">
         <x:is>
@@ -586,10 +570,8 @@
       <x:c r="E9" s="12" t="n">
         <x:v>0.199</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F9" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G9" s="12" t="inlineStr">
         <x:is>
@@ -617,10 +599,8 @@
       <x:c r="E10" s="12" t="n">
         <x:v>0.261</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F10" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G10" s="12" t="inlineStr">
         <x:is>
@@ -648,10 +628,8 @@
       <x:c r="E11" s="12" t="n">
         <x:v>0.161</x:v>
       </x:c>
-      <x:c r="F11" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F11" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G11" s="12" t="inlineStr">
         <x:is>
@@ -679,10 +657,8 @@
       <x:c r="E12" s="12" t="n">
         <x:v>0.102</x:v>
       </x:c>
-      <x:c r="F12" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F12" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G12" s="12" t="inlineStr">
         <x:is>
@@ -710,10 +686,8 @@
       <x:c r="E13" s="12" t="n">
         <x:v>0.191</x:v>
       </x:c>
-      <x:c r="F13" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F13" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G13" s="12" t="inlineStr">
         <x:is>
@@ -741,10 +715,8 @@
       <x:c r="E14" s="12" t="n">
         <x:v>0.035</x:v>
       </x:c>
-      <x:c r="F14" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F14" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G14" s="12" t="inlineStr">
         <x:is>
@@ -772,10 +744,8 @@
       <x:c r="E15" s="12" t="n">
         <x:v>0.188</x:v>
       </x:c>
-      <x:c r="F15" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F15" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G15" s="12" t="inlineStr">
         <x:is>
@@ -803,10 +773,8 @@
       <x:c r="E16" s="12" t="n">
         <x:v>0.15</x:v>
       </x:c>
-      <x:c r="F16" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F16" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G16" s="12" t="inlineStr">
         <x:is>
@@ -834,10 +802,8 @@
       <x:c r="E17" s="12" t="n">
         <x:v>0.08309999999999999</x:v>
       </x:c>
-      <x:c r="F17" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F17" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G17" s="12" t="inlineStr">
         <x:is>
@@ -865,10 +831,8 @@
       <x:c r="E18" s="12" t="n">
         <x:v>0.148</x:v>
       </x:c>
-      <x:c r="F18" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F18" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G18" s="12" t="inlineStr">
         <x:is>
@@ -896,10 +860,8 @@
       <x:c r="E19" s="12" t="n">
         <x:v>0.0669</x:v>
       </x:c>
-      <x:c r="F19" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F19" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G19" s="12" t="inlineStr">
         <x:is>
@@ -927,10 +889,8 @@
       <x:c r="E20" s="12" t="n">
         <x:v>0.194</x:v>
       </x:c>
-      <x:c r="F20" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F20" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G20" s="12" t="inlineStr">
         <x:is>
@@ -958,10 +918,8 @@
       <x:c r="E21" s="12" t="n">
         <x:v>0.135</x:v>
       </x:c>
-      <x:c r="F21" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F21" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G21" s="12" t="inlineStr">
         <x:is>
@@ -989,10 +947,8 @@
       <x:c r="E22" s="12" t="n">
         <x:v>0.116</x:v>
       </x:c>
-      <x:c r="F22" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F22" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G22" s="12" t="inlineStr">
         <x:is>
@@ -1020,10 +976,8 @@
       <x:c r="E23" s="12" t="n">
         <x:v>0.279</x:v>
       </x:c>
-      <x:c r="F23" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F23" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G23" s="12" t="inlineStr">
         <x:is>
@@ -1051,10 +1005,8 @@
       <x:c r="E24" s="12" t="n">
         <x:v>0.149</x:v>
       </x:c>
-      <x:c r="F24" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F24" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G24" s="12" t="inlineStr">
         <x:is>
@@ -1082,10 +1034,8 @@
       <x:c r="E25" s="12" t="n">
         <x:v>0.108</x:v>
       </x:c>
-      <x:c r="F25" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F25" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G25" s="12" t="inlineStr">
         <x:is>
@@ -1113,10 +1063,8 @@
       <x:c r="E26" s="12" t="n">
         <x:v>0.234</x:v>
       </x:c>
-      <x:c r="F26" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F26" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G26" s="12" t="inlineStr">
         <x:is>
@@ -1144,10 +1092,8 @@
       <x:c r="E27" s="12" t="n">
         <x:v>0.215</x:v>
       </x:c>
-      <x:c r="F27" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F27" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G27" s="12" t="inlineStr">
         <x:is>
@@ -1175,10 +1121,8 @@
       <x:c r="E28" s="12" t="n">
         <x:v>0.195</x:v>
       </x:c>
-      <x:c r="F28" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F28" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G28" s="12" t="inlineStr">
         <x:is>
@@ -1206,10 +1150,8 @@
       <x:c r="E29" s="12" t="n">
         <x:v>0.125</x:v>
       </x:c>
-      <x:c r="F29" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gained_after_mutation</x:t>
-        </x:is>
+      <x:c r="F29" s="12" t="str">
+        <x:v>gained_in_design</x:v>
       </x:c>
       <x:c r="G29" s="12" t="inlineStr">
         <x:is>
